--- a/artfynd/A 23008-2026 artfynd.xlsx
+++ b/artfynd/A 23008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95286102</v>
+        <v>134759689</v>
       </c>
       <c r="B2" t="n">
-        <v>79946</v>
+        <v>92647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnbråtstjärnen NNO om, Nrk</t>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468609</v>
+        <v>468692</v>
       </c>
       <c r="R2" t="n">
-        <v>6553316</v>
+        <v>6553572</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,12 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I kanten till hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,57 +771,639 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>kraftledningsgata invid myr</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>grånad stubbe</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Wood surface of dead wood # grånad, hård tallved # Pinus sylvestris # grånad stubbe</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>95286102</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen NNO om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>468609</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6553316</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kraftledningsgata invid myr</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>grånad stubbe</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Wood surface of dead wood # grånad, hård tallved # Pinus sylvestris # grånad stubbe</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134763586</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>04:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134763722</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>66 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134763633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>665 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134763733</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>99 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23008-2026 artfynd.xlsx
+++ b/artfynd/A 23008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134763633</v>
+        <v>135429497</v>
       </c>
       <c r="B6" t="n">
-        <v>57776</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1191,15 +1191,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468596</v>
+        <v>468647</v>
       </c>
       <c r="R6" t="n">
-        <v>6553436</v>
+        <v>6553386</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1238,27 +1247,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23:13</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>02:38</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>665 noteringar under perioden</t>
+          <t>Färsk bälgrop med stjärtfjäder fr tjädertupp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,32 +1284,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134763733</v>
+        <v>134763633</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1360,12 +1359,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>03:34</t>
+          <t>23:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,12 +1374,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>02:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>99 noteringar under perioden</t>
+          <t>665 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,6 +1403,128 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134763733</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>99 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23008-2026 artfynd.xlsx
+++ b/artfynd/A 23008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135429497</v>
+        <v>135443012</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,41 +1174,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1217,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468647</v>
+        <v>468686</v>
       </c>
       <c r="R6" t="n">
-        <v>6553386</v>
+        <v>6553593</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,17 +1233,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färsk bälgrop med stjärtfjäder fr tjädertupp.</t>
+          <t>Noterad 4 dagar, totalt 5 ggr under 8-dagarsperioden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134763633</v>
+        <v>135429497</v>
       </c>
       <c r="B7" t="n">
-        <v>57776</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,16 +1281,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102118</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1312,15 +1298,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1329,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468596</v>
+        <v>468647</v>
       </c>
       <c r="R7" t="n">
-        <v>6553436</v>
+        <v>6553386</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1359,27 +1354,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>23:13</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>02:38</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>665 noteringar under perioden</t>
+          <t>Färsk bälgrop med stjärtfjäder fr tjädertupp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,32 +1391,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134763733</v>
+        <v>134763633</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,12 +1466,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>03:34</t>
+          <t>23:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,12 +1481,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>02:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>99 noteringar under perioden</t>
+          <t>665 noteringar under perioden</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,6 +1510,575 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135442908</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterad 8 dagar och totalt 447 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135442821</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58415</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134763733</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>99 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135443086</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Noterad 4 dagar, totalt 59 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135443100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Noterad 8 dagar, totalt 282 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23008-2026 artfynd.xlsx
+++ b/artfynd/A 23008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95286102</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763586</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763722</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135443012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429497</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1510,6 +1545,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763633</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1622,6 +1662,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442908</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1733,6 +1778,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442821</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1967,6 +2022,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135443086</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2079,8 +2139,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135443100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23008-2026 artfynd.xlsx
+++ b/artfynd/A 23008-2026 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>135443012</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135429497</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>135442908</v>
       </c>
       <c r="B9" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>135442821</v>
       </c>
       <c r="B10" t="n">
-        <v>58415</v>
+        <v>58420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135443086</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135443100</v>
       </c>
       <c r="B13" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 23008-2026 artfynd.xlsx
+++ b/artfynd/A 23008-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134763633</v>
+        <v>135443012</v>
       </c>
       <c r="B6" t="n">
-        <v>57776</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,29 +1199,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1233,13 +1228,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468596</v>
+        <v>468686</v>
       </c>
       <c r="R6" t="n">
-        <v>6553436</v>
+        <v>6553593</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,27 +1258,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23:13</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>02:38</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>665 noteringar under perioden</t>
+          <t>Noterad 4 dagar, totalt 5 ggr under 8-dagarsperioden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,49 +1294,58 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134763633</t>
+          <t>https://artportalen.se/Sighting/135443012</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134763733</v>
+        <v>135429497</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1360,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468596</v>
+        <v>468647</v>
       </c>
       <c r="R7" t="n">
-        <v>6553436</v>
+        <v>6553386</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1390,27 +1384,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>03:34</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>99 noteringar under perioden</t>
+          <t>Färsk bälgrop med stjärtfjäder fr tjädertupp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,7 +1420,728 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135429497</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134763633</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>665 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134763633</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135442908</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57781</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterad 8 dagar och totalt 447 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442908</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135442821</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58420</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442821</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134763733</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468596</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553436</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>99 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134763733</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135443086</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Noterad 4 dagar, totalt 59 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135443086</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135443100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>468686</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6553593</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Noterad 8 dagar, totalt 282 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135443100</t>
         </is>
       </c>
     </row>
@@ -1448,6 +2153,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
